--- a/WorkBook/工作簿1.xlsx
+++ b/WorkBook/工作簿1.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="154">
   <si>
     <t>火炮型号</t>
   </si>
@@ -283,6 +283,18 @@
   </si>
   <si>
     <t>5=6</t>
+  </si>
+  <si>
+    <t>speed-2</t>
+  </si>
+  <si>
+    <t>speed-5</t>
+  </si>
+  <si>
+    <t>speed-8</t>
+  </si>
+  <si>
+    <t>sinking</t>
   </si>
   <si>
     <t>德国</t>
@@ -487,14 +499,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,6 +533,14 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1004,137 +1025,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1180,8 +1201,14 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2226,10 +2253,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="9" style="2"/>
+    <col min="1" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="10.375" style="2"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2258,7 +2287,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:18">
       <c r="A2" s="1">
         <v>1916</v>
       </c>
@@ -2286,11 +2315,36 @@
       <c r="I2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="J2" s="15">
+        <v>120</v>
+      </c>
+      <c r="K2" s="16">
+        <v>70</v>
+      </c>
+      <c r="L2" s="16">
+        <v>50</v>
+      </c>
+      <c r="M2" s="17">
+        <v>25</v>
+      </c>
+      <c r="O2" s="2">
+        <f>J2/5</f>
+        <v>24</v>
+      </c>
+      <c r="P2" s="2">
+        <f>K2/5</f>
+        <v>14</v>
+      </c>
+      <c r="Q2" s="2">
+        <f>L2/5</f>
+        <v>10</v>
+      </c>
+      <c r="R2" s="2">
+        <f>M2/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1">
         <v>1916</v>
       </c>
@@ -2318,11 +2372,39 @@
       <c r="I3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="J3" s="15">
+        <v>125</v>
+      </c>
+      <c r="K3" s="16">
+        <f>J3*0.6</f>
+        <v>75</v>
+      </c>
+      <c r="L3" s="16">
+        <f>J3*0.4</f>
+        <v>50</v>
+      </c>
+      <c r="M3" s="17">
+        <f>J3*0.2</f>
+        <v>25</v>
+      </c>
+      <c r="O3" s="2">
+        <f t="shared" ref="O3:O32" si="0">J3/5</f>
+        <v>25</v>
+      </c>
+      <c r="P3" s="2">
+        <f t="shared" ref="P3:P19" si="1">K3/5</f>
+        <v>15</v>
+      </c>
+      <c r="Q3" s="2">
+        <f>L3/5</f>
+        <v>10</v>
+      </c>
+      <c r="R3" s="2">
+        <f>M3/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="1">
         <v>1916</v>
       </c>
@@ -2350,11 +2432,36 @@
       <c r="I4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="J4" s="15">
+        <v>130</v>
+      </c>
+      <c r="K4" s="16">
+        <v>80</v>
+      </c>
+      <c r="L4" s="16">
+        <v>50</v>
+      </c>
+      <c r="M4" s="17">
+        <v>25</v>
+      </c>
+      <c r="O4" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="P4" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>L4/5</f>
+        <v>10</v>
+      </c>
+      <c r="R4" s="2">
+        <f>M4/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
         <v>1916</v>
       </c>
@@ -2382,11 +2489,36 @@
       <c r="I5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="J5" s="15">
+        <v>130</v>
+      </c>
+      <c r="K5" s="16">
+        <v>80</v>
+      </c>
+      <c r="L5" s="16">
+        <v>50</v>
+      </c>
+      <c r="M5" s="17">
+        <v>25</v>
+      </c>
+      <c r="O5" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="P5" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="Q5" s="2">
+        <f>L5/5</f>
+        <v>10</v>
+      </c>
+      <c r="R5" s="2">
+        <f>M5/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>1916</v>
       </c>
@@ -2414,11 +2546,36 @@
       <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="J6" s="15">
+        <v>130</v>
+      </c>
+      <c r="K6" s="16">
+        <v>80</v>
+      </c>
+      <c r="L6" s="16">
+        <v>50</v>
+      </c>
+      <c r="M6" s="17">
+        <v>25</v>
+      </c>
+      <c r="O6" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>L6/5</f>
+        <v>10</v>
+      </c>
+      <c r="R6" s="2">
+        <f>M6/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
         <v>1916</v>
       </c>
@@ -2446,11 +2603,36 @@
       <c r="I7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="J7" s="15">
+        <v>145</v>
+      </c>
+      <c r="K7" s="16">
+        <v>90</v>
+      </c>
+      <c r="L7" s="16">
+        <v>60</v>
+      </c>
+      <c r="M7" s="17">
+        <v>30</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>L7/5</f>
+        <v>12</v>
+      </c>
+      <c r="R7" s="2">
+        <f>M7/5</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
         <v>1916</v>
       </c>
@@ -2478,11 +2660,36 @@
       <c r="I8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="J8" s="15">
+        <v>160</v>
+      </c>
+      <c r="K8" s="16">
+        <v>95</v>
+      </c>
+      <c r="L8" s="16">
+        <v>65</v>
+      </c>
+      <c r="M8" s="17">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>L8/5</f>
+        <v>13</v>
+      </c>
+      <c r="R8" s="2">
+        <f>M8/5</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
         <v>1916</v>
       </c>
@@ -2510,11 +2717,40 @@
       <c r="I9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="J9" s="15">
+        <v>175</v>
+      </c>
+      <c r="K9" s="16">
+        <f>J9*0.6</f>
+        <v>105</v>
+      </c>
+      <c r="L9" s="16">
+        <f>J9*0.4</f>
+        <v>70</v>
+      </c>
+      <c r="M9" s="17">
+        <f>J9*0.2</f>
+        <v>35</v>
+      </c>
+      <c r="N9" s="17"/>
+      <c r="O9" s="2">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>L9/5</f>
+        <v>14</v>
+      </c>
+      <c r="R9" s="2">
+        <f>M9/5</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
         <v>1916</v>
       </c>
@@ -2542,11 +2778,37 @@
       <c r="I10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="J10" s="15">
+        <v>145</v>
+      </c>
+      <c r="K10" s="16">
+        <v>90</v>
+      </c>
+      <c r="L10" s="16">
+        <v>60</v>
+      </c>
+      <c r="M10" s="17">
+        <v>30</v>
+      </c>
+      <c r="N10" s="17"/>
+      <c r="O10" s="2">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="Q10" s="2">
+        <f>L10/5</f>
+        <v>12</v>
+      </c>
+      <c r="R10" s="2">
+        <f>M10/5</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
         <v>1916</v>
       </c>
@@ -2574,11 +2836,37 @@
       <c r="I11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="J11" s="15">
+        <v>185</v>
+      </c>
+      <c r="K11" s="16">
+        <v>110</v>
+      </c>
+      <c r="L11" s="16">
+        <v>75</v>
+      </c>
+      <c r="M11" s="17">
+        <v>35</v>
+      </c>
+      <c r="N11" s="17"/>
+      <c r="O11" s="2">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="P11" s="2">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>L11/5</f>
+        <v>15</v>
+      </c>
+      <c r="R11" s="2">
+        <f>M11/5</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="1">
         <v>1916</v>
       </c>
@@ -2606,11 +2894,37 @@
       <c r="I12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="J12" s="15">
+        <v>180</v>
+      </c>
+      <c r="K12" s="16">
+        <v>110</v>
+      </c>
+      <c r="L12" s="16">
+        <v>70</v>
+      </c>
+      <c r="M12" s="17">
+        <v>35</v>
+      </c>
+      <c r="N12" s="17"/>
+      <c r="O12" s="2">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="P12" s="2">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>L12/5</f>
+        <v>14</v>
+      </c>
+      <c r="R12" s="2">
+        <f>M12/5</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
         <v>1916</v>
       </c>
@@ -2638,11 +2952,37 @@
       <c r="I13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="J13" s="15">
+        <v>190</v>
+      </c>
+      <c r="K13" s="16">
+        <v>115</v>
+      </c>
+      <c r="L13" s="16">
+        <v>75</v>
+      </c>
+      <c r="M13" s="17">
+        <v>40</v>
+      </c>
+      <c r="N13" s="17"/>
+      <c r="O13" s="2">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="P13" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q13" s="2">
+        <f>L13/5</f>
+        <v>15</v>
+      </c>
+      <c r="R13" s="2">
+        <f>M13/5</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="1">
         <v>1916</v>
       </c>
@@ -2670,11 +3010,40 @@
       <c r="I14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="J14" s="15">
+        <v>200</v>
+      </c>
+      <c r="K14" s="16">
+        <f>J14*0.6</f>
+        <v>120</v>
+      </c>
+      <c r="L14" s="16">
+        <f>J14*0.4</f>
+        <v>80</v>
+      </c>
+      <c r="M14" s="17">
+        <f>J14*0.2</f>
+        <v>40</v>
+      </c>
+      <c r="N14" s="17"/>
+      <c r="O14" s="2">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="P14" s="2">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>L14/5</f>
+        <v>16</v>
+      </c>
+      <c r="R14" s="2">
+        <f>M14/5</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1">
         <v>1916</v>
       </c>
@@ -2702,11 +3071,37 @@
       <c r="I15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="J15" s="15">
+        <v>115</v>
+      </c>
+      <c r="K15" s="16">
+        <v>70</v>
+      </c>
+      <c r="L15" s="16">
+        <v>45</v>
+      </c>
+      <c r="M15" s="17">
+        <v>25</v>
+      </c>
+      <c r="N15" s="17"/>
+      <c r="O15" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="P15" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>L15/5</f>
+        <v>9</v>
+      </c>
+      <c r="R15" s="2">
+        <f>M15/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="1">
         <v>1916</v>
       </c>
@@ -2734,11 +3129,40 @@
       <c r="I16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="J16" s="15">
+        <v>125</v>
+      </c>
+      <c r="K16" s="16">
+        <f>J16*0.6</f>
+        <v>75</v>
+      </c>
+      <c r="L16" s="16">
+        <f>J16*0.4</f>
+        <v>50</v>
+      </c>
+      <c r="M16" s="17">
+        <f>J16*0.2</f>
+        <v>25</v>
+      </c>
+      <c r="N16" s="17"/>
+      <c r="O16" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="P16" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q16" s="2">
+        <f>L16/5</f>
+        <v>10</v>
+      </c>
+      <c r="R16" s="2">
+        <f>M16/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
@@ -2760,11 +3184,40 @@
       <c r="I17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="J17" s="15">
+        <v>125</v>
+      </c>
+      <c r="K17" s="16">
+        <f>J17*0.6</f>
+        <v>75</v>
+      </c>
+      <c r="L17" s="16">
+        <f>J17*0.4</f>
+        <v>50</v>
+      </c>
+      <c r="M17" s="17">
+        <f>J17*0.2</f>
+        <v>25</v>
+      </c>
+      <c r="N17" s="17"/>
+      <c r="O17" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>L17/5</f>
+        <v>10</v>
+      </c>
+      <c r="R17" s="2">
+        <f>M17/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <v>1916</v>
       </c>
@@ -2792,11 +3245,37 @@
       <c r="I18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="J18" s="15">
+        <v>170</v>
+      </c>
+      <c r="K18" s="16">
+        <v>100</v>
+      </c>
+      <c r="L18" s="16">
+        <v>70</v>
+      </c>
+      <c r="M18" s="17">
+        <v>35</v>
+      </c>
+      <c r="N18" s="17"/>
+      <c r="O18" s="2">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="P18" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>L18/5</f>
+        <v>14</v>
+      </c>
+      <c r="R18" s="2">
+        <f>M18/5</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <v>1916</v>
       </c>
@@ -2824,21 +3303,56 @@
       <c r="I19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-    </row>
-    <row r="20" spans="5:12">
+      <c r="J19" s="15">
+        <v>185</v>
+      </c>
+      <c r="K19" s="16">
+        <v>110</v>
+      </c>
+      <c r="L19" s="16">
+        <v>75</v>
+      </c>
+      <c r="M19" s="17">
+        <v>40</v>
+      </c>
+      <c r="N19" s="17"/>
+      <c r="O19" s="2">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="P19" s="2">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q19" s="2">
+        <f>L19/5</f>
+        <v>15</v>
+      </c>
+      <c r="R19" s="2">
+        <f>M19/5</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="5:18">
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" s="2"/>
       <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="P20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2848,22 +3362,22 @@
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="R21" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1">
         <v>1916</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E22" s="14">
         <v>6</v>
@@ -2878,24 +3392,50 @@
         <v>5</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-    </row>
-    <row r="23" spans="1:12">
+        <v>91</v>
+      </c>
+      <c r="J22" s="15">
+        <v>120</v>
+      </c>
+      <c r="K22" s="16">
+        <v>65</v>
+      </c>
+      <c r="L22" s="16">
+        <v>40</v>
+      </c>
+      <c r="M22" s="17">
+        <v>20</v>
+      </c>
+      <c r="N22" s="14"/>
+      <c r="O22" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" ref="P20:P32" si="2">K22/5</f>
+        <v>13</v>
+      </c>
+      <c r="Q22" s="2">
+        <f>L22/5</f>
+        <v>8</v>
+      </c>
+      <c r="R22" s="2">
+        <f>M22/5</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="1">
         <v>1916</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E23" s="14">
         <v>7</v>
@@ -2910,24 +3450,50 @@
         <v>6</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-    </row>
-    <row r="24" spans="1:12">
+        <v>91</v>
+      </c>
+      <c r="J23" s="15">
+        <v>145</v>
+      </c>
+      <c r="K23" s="16">
+        <v>80</v>
+      </c>
+      <c r="L23" s="16">
+        <v>50</v>
+      </c>
+      <c r="M23" s="17">
+        <v>20</v>
+      </c>
+      <c r="N23" s="14"/>
+      <c r="O23" s="2">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="P23" s="2">
+        <f>K23/5</f>
+        <v>16</v>
+      </c>
+      <c r="Q23" s="2">
+        <f>L23/5</f>
+        <v>10</v>
+      </c>
+      <c r="R23" s="2">
+        <f>M23/5</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" s="1">
         <v>1916</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E24" s="14">
         <v>9</v>
@@ -2942,24 +3508,50 @@
         <v>8</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-    </row>
-    <row r="25" spans="1:12">
+        <v>96</v>
+      </c>
+      <c r="J24" s="15">
+        <v>155</v>
+      </c>
+      <c r="K24" s="16">
+        <v>85</v>
+      </c>
+      <c r="L24" s="16">
+        <v>55</v>
+      </c>
+      <c r="M24" s="17">
+        <v>25</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="2">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="Q24" s="2">
+        <f>L24/5</f>
+        <v>11</v>
+      </c>
+      <c r="R24" s="2">
+        <f>M24/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="1">
         <v>1916</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E25" s="14">
         <v>9</v>
@@ -2974,24 +3566,50 @@
         <v>8</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-    </row>
-    <row r="26" spans="1:12">
+        <v>96</v>
+      </c>
+      <c r="J25" s="15">
+        <v>165</v>
+      </c>
+      <c r="K25" s="16">
+        <v>90</v>
+      </c>
+      <c r="L25" s="16">
+        <v>60</v>
+      </c>
+      <c r="M25" s="17">
+        <v>25</v>
+      </c>
+      <c r="N25" s="14"/>
+      <c r="O25" s="2">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="Q25" s="2">
+        <f>L25/5</f>
+        <v>12</v>
+      </c>
+      <c r="R25" s="2">
+        <f>M25/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1">
         <v>1916</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E26" s="14">
         <v>9</v>
@@ -3006,24 +3624,50 @@
         <v>8</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-    </row>
-    <row r="27" spans="1:12">
+        <v>101</v>
+      </c>
+      <c r="J26" s="15">
+        <v>185</v>
+      </c>
+      <c r="K26" s="16">
+        <v>100</v>
+      </c>
+      <c r="L26" s="16">
+        <v>65</v>
+      </c>
+      <c r="M26" s="17">
+        <v>30</v>
+      </c>
+      <c r="N26" s="14"/>
+      <c r="O26" s="2">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="P26" s="2">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="Q26" s="2">
+        <f>L26/5</f>
+        <v>13</v>
+      </c>
+      <c r="R26" s="2">
+        <f>M26/5</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" s="1">
         <v>1916</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E27" s="14">
         <v>5</v>
@@ -3038,24 +3682,50 @@
         <v>4</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-    </row>
-    <row r="28" spans="1:12">
+        <v>104</v>
+      </c>
+      <c r="J27" s="15">
+        <v>125</v>
+      </c>
+      <c r="K27" s="16">
+        <v>70</v>
+      </c>
+      <c r="L27" s="16">
+        <v>45</v>
+      </c>
+      <c r="M27" s="17">
+        <v>20</v>
+      </c>
+      <c r="N27" s="14"/>
+      <c r="O27" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="P27" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="Q27" s="2">
+        <f>L27/5</f>
+        <v>9</v>
+      </c>
+      <c r="R27" s="2">
+        <f>M27/5</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1">
         <v>1916</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E28" s="14">
         <v>7</v>
@@ -3070,30 +3740,56 @@
         <v>6</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-    </row>
-    <row r="29" spans="1:12">
+        <v>104</v>
+      </c>
+      <c r="J28" s="15">
+        <v>150</v>
+      </c>
+      <c r="K28" s="16">
+        <v>80</v>
+      </c>
+      <c r="L28" s="16">
+        <v>55</v>
+      </c>
+      <c r="M28" s="17">
+        <v>25</v>
+      </c>
+      <c r="N28" s="14"/>
+      <c r="O28" s="2">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="P28" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="Q28" s="2">
+        <f>L28/5</f>
+        <v>11</v>
+      </c>
+      <c r="R28" s="2">
+        <f>M28/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1">
         <v>1916</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E29" s="14">
         <v>9</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
@@ -3104,22 +3800,48 @@
       <c r="I29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="J29" s="15">
+        <v>165</v>
+      </c>
+      <c r="K29" s="16">
+        <v>90</v>
+      </c>
+      <c r="L29" s="16">
+        <v>60</v>
+      </c>
+      <c r="M29" s="17">
+        <v>25</v>
+      </c>
+      <c r="N29" s="14"/>
+      <c r="O29" s="2">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="P29" s="2">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="Q29" s="2">
+        <f>L29/5</f>
+        <v>12</v>
+      </c>
+      <c r="R29" s="2">
+        <f>M29/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1">
         <v>1916</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E30" s="14">
         <v>9</v>
@@ -3128,7 +3850,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H30" s="14">
         <v>8</v>
@@ -3136,22 +3858,108 @@
       <c r="I30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="J30" s="15">
+        <v>175</v>
+      </c>
+      <c r="K30" s="16">
+        <v>95</v>
+      </c>
+      <c r="L30" s="16">
+        <v>60</v>
+      </c>
+      <c r="M30" s="17">
+        <v>25</v>
+      </c>
+      <c r="N30" s="14"/>
+      <c r="O30" s="2">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="P30" s="2">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="Q30" s="2">
+        <f>L30/5</f>
+        <v>12</v>
+      </c>
+      <c r="R30" s="2">
+        <f>M30/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1">
         <v>1916</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="J31" s="17">
+        <v>85</v>
+      </c>
+      <c r="K31" s="16">
+        <v>45</v>
+      </c>
+      <c r="L31" s="16">
+        <v>30</v>
+      </c>
+      <c r="M31" s="17">
+        <v>15</v>
+      </c>
+      <c r="N31" s="14"/>
+      <c r="O31" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="P31" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="Q31" s="2">
+        <f>L31/5</f>
+        <v>6</v>
+      </c>
+      <c r="R31" s="2">
+        <f>M31/5</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="10:18">
+      <c r="J32" s="17">
+        <v>85</v>
+      </c>
+      <c r="K32" s="16">
+        <v>45</v>
+      </c>
+      <c r="L32" s="16">
+        <v>30</v>
+      </c>
+      <c r="M32" s="17">
+        <v>15</v>
+      </c>
+      <c r="N32" s="14"/>
+      <c r="O32" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="P32" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="Q32" s="2">
+        <f>L32/5</f>
+        <v>6</v>
+      </c>
+      <c r="R32" s="2">
+        <f>M32/5</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3173,7 +3981,7 @@
   <sheetData>
     <row r="1" ht="14.25" spans="1:5">
       <c r="A1" s="12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>40</v>
@@ -3195,10 +4003,10 @@
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" ht="28.5" spans="1:5">
@@ -3206,16 +4014,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:5">
@@ -3223,16 +4031,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" ht="57" spans="1:5">
@@ -3240,16 +4048,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="57" spans="1:5">
@@ -3257,16 +4065,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="28.5" spans="1:5">
@@ -3277,13 +4085,13 @@
         <v>69</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="28.5" spans="1:5">
@@ -3291,13 +4099,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E8" s="12"/>
     </row>
@@ -3307,7 +4115,7 @@
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
@@ -3638,10 +4446,10 @@
     </row>
     <row r="37" ht="14.25" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C37" s="5">
         <v>283</v>
@@ -3650,7 +4458,7 @@
     <row r="38" ht="14.25" spans="1:3">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C38" s="7">
         <v>321.966</v>
@@ -3659,7 +4467,7 @@
     <row r="39" ht="14.25" spans="1:3">
       <c r="A39" s="6"/>
       <c r="B39" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C39" s="7">
         <v>280</v>
@@ -3668,7 +4476,7 @@
     <row r="40" ht="14.25" spans="1:3">
       <c r="A40" s="8"/>
       <c r="B40" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C40" s="9">
         <v>200</v>
@@ -3691,10 +4499,10 @@
     </row>
     <row r="44" ht="14.25" spans="1:3">
       <c r="A44" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C44" s="7">
         <v>285</v>
@@ -3703,7 +4511,7 @@
     <row r="45" ht="14.25" spans="1:3">
       <c r="A45" s="6"/>
       <c r="B45" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C45" s="7">
         <v>205.412</v>
@@ -3712,7 +4520,7 @@
     <row r="46" ht="14.25" spans="1:3">
       <c r="A46" s="6"/>
       <c r="B46" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C46" s="7">
         <v>234.262</v>
@@ -3740,10 +4548,10 @@
     </row>
     <row r="51" ht="14.25" spans="1:3">
       <c r="A51" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="C51" s="5">
         <v>345</v>
@@ -3752,7 +4560,7 @@
     <row r="52" ht="14.25" spans="1:3">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C52" s="7">
         <v>293.116</v>
@@ -3761,7 +4569,7 @@
     <row r="53" ht="14.25" spans="1:3">
       <c r="A53" s="6"/>
       <c r="B53" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C53" s="7">
         <v>264.266</v>
@@ -3770,7 +4578,7 @@
     <row r="54" ht="14.25" spans="1:3">
       <c r="A54" s="6"/>
       <c r="B54" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C54" s="7">
         <v>293.116</v>
@@ -3779,7 +4587,7 @@
     <row r="55" ht="14.25" spans="1:3">
       <c r="A55" s="6"/>
       <c r="B55" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C55" s="7">
         <v>321.966</v>
@@ -3788,7 +4596,7 @@
     <row r="56" ht="14.25" spans="1:3">
       <c r="A56" s="8"/>
       <c r="B56" s="9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C56" s="9">
         <v>351.97</v>
@@ -3797,7 +4605,7 @@
     <row r="57" ht="14.25" spans="1:3">
       <c r="A57" s="6"/>
       <c r="B57" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C57" s="7">
         <v>345</v>
@@ -3806,7 +4614,7 @@
     <row r="58" ht="14.25" spans="1:3">
       <c r="A58" s="6"/>
       <c r="B58" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C58" s="7">
         <v>305</v>
@@ -3815,7 +4623,7 @@
     <row r="59" ht="14.25" spans="1:3">
       <c r="A59" s="6"/>
       <c r="B59" s="7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C59" s="7">
         <v>254</v>
@@ -3824,7 +4632,7 @@
     <row r="60" ht="14.25" spans="1:3">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C60" s="7">
         <v>229</v>
@@ -3832,10 +4640,10 @@
     </row>
     <row r="61" ht="14.25" spans="1:3">
       <c r="A61" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="C61" s="5">
         <v>410.824</v>
@@ -3844,7 +4652,7 @@
     <row r="62" ht="14.25" spans="1:3">
       <c r="A62" s="6"/>
       <c r="B62" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C62" s="7">
         <v>395.822</v>
@@ -3853,7 +4661,7 @@
     <row r="63" ht="14.25" spans="1:3">
       <c r="A63" s="6"/>
       <c r="B63" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C63" s="7">
         <v>390</v>
@@ -3862,7 +4670,7 @@
     <row r="64" ht="14.25" spans="1:3">
       <c r="A64" s="6"/>
       <c r="B64" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C64" s="7">
         <v>350</v>
@@ -3871,7 +4679,7 @@
     <row r="65" ht="14.25" spans="1:3">
       <c r="A65" s="6"/>
       <c r="B65" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C65" s="7">
         <v>265</v>
@@ -3880,7 +4688,7 @@
     <row r="66" ht="14.25" spans="1:3">
       <c r="A66" s="6"/>
       <c r="B66" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C66" s="7">
         <v>220</v>
@@ -3912,7 +4720,7 @@
         <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
@@ -4221,13 +5029,13 @@
         <v>1916</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>119</v>
@@ -4238,13 +5046,13 @@
         <v>1916</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E22">
         <v>144</v>
@@ -4255,13 +5063,13 @@
         <v>1916</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E23">
         <v>156</v>
@@ -4272,13 +5080,13 @@
         <v>1916</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E24">
         <v>165</v>
@@ -4289,13 +5097,13 @@
         <v>1916</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>184</v>
@@ -4306,13 +5114,13 @@
         <v>1916</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E26">
         <v>123</v>
@@ -4323,13 +5131,13 @@
         <v>1916</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E27">
         <v>147</v>
@@ -4340,13 +5148,13 @@
         <v>1916</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E28">
         <v>162</v>
@@ -4357,13 +5165,13 @@
         <v>1916</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E29">
         <v>175</v>
@@ -4374,13 +5182,13 @@
         <v>1916</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E30">
         <v>83</v>
